--- a/src-tauri/samples/mame/06_mame_plate_layout.xlsx
+++ b/src-tauri/samples/mame/06_mame_plate_layout.xlsx
@@ -467,7 +467,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Q232A</t>
+          <t>S65T</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -479,7 +479,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Q232A</t>
+          <t>S65T</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -491,7 +491,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Q232A</t>
+          <t>S65T</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -503,7 +503,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Y233A</t>
+          <t>Y66H</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -515,7 +515,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Y233A</t>
+          <t>Y66H</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -527,7 +527,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Y233A</t>
+          <t>Y66H</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -539,7 +539,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A40P</t>
+          <t>T203Y</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -551,7 +551,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A40P</t>
+          <t>T203Y</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -563,7 +563,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A40P</t>
+          <t>T203Y</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -575,7 +575,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>E61Y</t>
+          <t>F64L</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -587,7 +587,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>E61Y</t>
+          <t>F64L</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -599,7 +599,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>E61Y</t>
+          <t>F64L</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -611,7 +611,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>L150V</t>
+          <t>A206K</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -623,7 +623,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>L150V</t>
+          <t>A206K</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -635,7 +635,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>L150V</t>
+          <t>A206K</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -647,7 +647,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A40P_E61Y</t>
+          <t>S65A</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -659,7 +659,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A40P_E61Y</t>
+          <t>S65A</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -671,7 +671,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A40P_E61Y</t>
+          <t>S65A</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">

--- a/src-tauri/samples/mame/06_mame_plate_layout.xlsx
+++ b/src-tauri/samples/mame/06_mame_plate_layout.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Plate Layout" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Plate Layout" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B23"/>
+  <dimension ref="A1:B12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>WT</t>
+          <t>Y67H</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -443,250 +443,118 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>WT</t>
+          <t>F100S</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>A2</t>
+          <t>B1</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>WT</t>
+          <t>S148P</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>A3</t>
+          <t>C1</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>S65T</t>
+          <t>H149D</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>A4</t>
+          <t>D1</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>S65T</t>
+          <t>M154T</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>A5</t>
+          <t>E1</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>S65T</t>
+          <t>V164A</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>A6</t>
+          <t>F1</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Y66H</t>
+          <t>I168T</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>B1</t>
+          <t>G1</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Y66H</t>
+          <t>T204Y</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>B2</t>
+          <t>H1</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Y66H</t>
+          <t>S206T</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>B3</t>
+          <t>A2</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>T203Y</t>
+          <t>A207K</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>B4</t>
+          <t>B2</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>T203Y</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
-        <is>
-          <t>B5</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>T203Y</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>B6</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>F64L</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>C1</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>F64L</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>C2</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>F64L</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>C3</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>A206K</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>C4</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>A206K</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>C5</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>A206K</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>C6</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>S65A</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>D1</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>S65A</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>D2</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>S65A</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>D3</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>blank</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
         <is>
           <t>H12</t>
         </is>

--- a/src-tauri/samples/mame/06_mame_plate_layout.xlsx
+++ b/src-tauri/samples/mame/06_mame_plate_layout.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Y67H</t>
+          <t>F28A</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -443,7 +443,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>F100S</t>
+          <t>H78A</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -455,7 +455,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>S148P</t>
+          <t>A88V</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -467,7 +467,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>H149D</t>
+          <t>R97A</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -479,7 +479,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>M154T</t>
+          <t>I124A</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -491,7 +491,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>V164A</t>
+          <t>N150A</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -503,7 +503,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>I168T</t>
+          <t>K163A</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -515,7 +515,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>T204Y</t>
+          <t>G175A</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -527,7 +527,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>S206T</t>
+          <t>G190A</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -539,7 +539,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A207K</t>
+          <t>H200A</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">

--- a/src-tauri/samples/mame/06_mame_plate_layout.xlsx
+++ b/src-tauri/samples/mame/06_mame_plate_layout.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:B18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -551,10 +551,82 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>Q205A</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>C2</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>K210A</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>D2</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>K215A</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>A227V</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>F2</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>D235A</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>G2</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>K239A</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>WT</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>H12</t>
         </is>
